--- a/test/GeoInput.xlsx
+++ b/test/GeoInput.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TRNSYS18\TRNLib\CallingPython-Cffi\Examples\08b-PreSim_ParallelSyncBoreholes\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TRNSYS18\TRNLib\CallingPython-Cffi\Examples\08b-PreSim_ParallelSyncBoreholes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F99AF09-6290-4AD2-AC93-BCAA86F290AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5613532B-9F1E-49A0-BB51-FF7D6BAEA39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Borehole" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>H [m]</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>The first 2 years should be given as historical load. The 3 year is the one simulated</t>
+  </si>
+  <si>
+    <t>Tg [degC]</t>
+  </si>
+  <si>
+    <t>Rb [mK/W]</t>
   </si>
 </sst>
 </file>
@@ -468,7 +474,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07A9F8B-7467-45FD-B3CE-3E6B9983E5DA}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="1"/>
@@ -476,7 +482,7 @@
     <col min="3" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -486,8 +492,14 @@
       <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -496,6 +508,12 @@
       </c>
       <c r="C2" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
